--- a/artfynd/A 50930-2020 artfynd.xlsx
+++ b/artfynd/A 50930-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50930-2020 artfynd.xlsx
+++ b/artfynd/A 50930-2020 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74153085</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452023.7066121025</v>
+        <v>452024</v>
       </c>
       <c r="R2" t="n">
-        <v>6400063.964781202</v>
+        <v>6400064</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1977-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1977-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,12 +785,7 @@
         <v>74207957</v>
       </c>
       <c r="B3" t="n">
-        <v>104654</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452023.7066121025</v>
+        <v>452024</v>
       </c>
       <c r="R3" t="n">
-        <v>6400063.964781202</v>
+        <v>6400064</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +850,9 @@
           <t>1977-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1977-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -926,12 +896,7 @@
         <v>74411229</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452023.7066121025</v>
+        <v>452024</v>
       </c>
       <c r="R4" t="n">
-        <v>6400063.964781202</v>
+        <v>6400064</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,19 +961,9 @@
           <t>1977-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1977-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1052,12 +1007,7 @@
         <v>74478656</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452023.7066121025</v>
+        <v>452024</v>
       </c>
       <c r="R5" t="n">
-        <v>6400063.964781202</v>
+        <v>6400064</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1122,19 +1072,9 @@
           <t>1977-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1977-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1178,12 +1118,7 @@
         <v>74552203</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452023.7066121025</v>
+        <v>452024</v>
       </c>
       <c r="R6" t="n">
-        <v>6400063.964781202</v>
+        <v>6400064</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1248,19 +1183,9 @@
           <t>1977-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1977-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1304,12 +1229,7 @@
         <v>74560821</v>
       </c>
       <c r="B7" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106991</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452023.7066121025</v>
+        <v>452024</v>
       </c>
       <c r="R7" t="n">
-        <v>6400063.964781202</v>
+        <v>6400064</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1374,19 +1294,9 @@
           <t>1977-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1977-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 50930-2020 artfynd.xlsx
+++ b/artfynd/A 50930-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153085</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74207957</v>
       </c>
       <c r="B3" t="n">
-        <v>107096</v>
+        <v>107105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74411229</v>
       </c>
       <c r="B4" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74478656</v>
       </c>
       <c r="B5" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>74552203</v>
       </c>
       <c r="B6" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>74560821</v>
       </c>
       <c r="B7" t="n">
-        <v>106991</v>
+        <v>107000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50930-2020 artfynd.xlsx
+++ b/artfynd/A 50930-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153085</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74207957</v>
       </c>
       <c r="B3" t="n">
-        <v>107105</v>
+        <v>107110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74411229</v>
       </c>
       <c r="B4" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74478656</v>
       </c>
       <c r="B5" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>74552203</v>
       </c>
       <c r="B6" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>74560821</v>
       </c>
       <c r="B7" t="n">
-        <v>107000</v>
+        <v>107005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50930-2020 artfynd.xlsx
+++ b/artfynd/A 50930-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153085</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74207957</v>
       </c>
       <c r="B3" t="n">
-        <v>107110</v>
+        <v>107138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74411229</v>
       </c>
       <c r="B4" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74478656</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>74552203</v>
       </c>
       <c r="B6" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>74560821</v>
       </c>
       <c r="B7" t="n">
-        <v>107005</v>
+        <v>107033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50930-2020 artfynd.xlsx
+++ b/artfynd/A 50930-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153085</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74207957</v>
       </c>
       <c r="B3" t="n">
-        <v>107138</v>
+        <v>107144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74411229</v>
       </c>
       <c r="B4" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74478656</v>
       </c>
       <c r="B5" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>74552203</v>
       </c>
       <c r="B6" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>74560821</v>
       </c>
       <c r="B7" t="n">
-        <v>107033</v>
+        <v>107039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50930-2020 artfynd.xlsx
+++ b/artfynd/A 50930-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153085</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74207957</v>
       </c>
       <c r="B3" t="n">
-        <v>107144</v>
+        <v>107151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74411229</v>
       </c>
       <c r="B4" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74478656</v>
       </c>
       <c r="B5" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>74552203</v>
       </c>
       <c r="B6" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>74560821</v>
       </c>
       <c r="B7" t="n">
-        <v>107039</v>
+        <v>107046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
